--- a/Result/checksun_type/網路IC.xlsx
+++ b/Result/checksun_type/網路IC.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>45.73</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>47.69</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>141265.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>225541.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>225541.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>354816.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>754339.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>754339.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-185798.2351603996</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>141265</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>141265.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>46.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.19</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>163516.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>258309.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>258309.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>470557.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>752823.34</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>752823.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-183529.3073428617</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>163516</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>163516.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>46.67</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.51</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>127895.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>309053.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>309053</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>863925.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>750375.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>750375.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-176117.3994841338</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>127895</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>127895.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>48.11</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.22</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>230457.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>377395.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>377395.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1038086.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>748807.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>748807.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-155422.5168472321</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>230457</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>230457.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.68</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.12</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>464574.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>395693.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>395693.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1129464.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>745315.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>745315.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-131296.3803356857</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>464574</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>464574.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>51.76000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>305106.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>484092.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>484092</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1175832.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>737857.46</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>737857.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-117225.2788786306</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>305106</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>305106.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>53.74000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>46.77</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>417233.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>682806.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>682806</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1192750.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>732695.38</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>732695.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-75851.23112288641</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>417233</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>417233.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>55.38</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.54</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>469607.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1418798.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1418798.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1210220.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>725481.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>725481.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-26050.08321743459</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>469607</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>469607.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>56.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.24</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.24</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>321946.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1698777.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1698777.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1236211.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>719386.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>719386.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>40413.27390526235</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>321946</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>321946.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>51.89</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>906568.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1863235.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1863235</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1401013.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>715148.3</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>715148.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>149738.4171553557</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>906568</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>906568.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>56.44</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.65</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1298676.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1867572.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1867572.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1665281.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>698393.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>698393.9399999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>237931.3211856545</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1298676</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1298676.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2767</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2040</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7527</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2843</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>8850</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4645</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2921</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6307</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>20919</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>13648</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>9458</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>13919</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>14252</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>34781</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4464</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>85.97999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>89.87</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>95.2</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>11375.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7178.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7178</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>8374.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>13947.82</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>13947.82</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-585.0773092036461</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>11375</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>11375.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>85.44000000000001</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>90.36</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>95.37</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>95.37</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>6678.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6058.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6058.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>8154.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>14227.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>14227.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1011.350274117645</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>6678</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>6678.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>85.78</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>91.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>95.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>95.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3344.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>7338.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>7338.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>8012.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>14403.68</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>14403.68</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1080.941999919158</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3344</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3344.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>86.44</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>91.78</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>95.9</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>8809.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>8286.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>8286</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>8693.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>14904.86</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>14904.86</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-784.5393939242058</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>8809</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>8809.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>87.44000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>92.51</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>96.23</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5684.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>8940.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>8940.799999999999</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>8390.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>15322.38</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>15322.38</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-918.6235498626957</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5684</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5684.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>88.18</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>93.19</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>96.5</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>96.5</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>5779.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>9570.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>9570</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>8442.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>16104.88</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>16104.88</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-742.5429315654419</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5779</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5779.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>89.14</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>93.88</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>96.72</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>96.72</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>13075.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>10250.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>10250.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>8727.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>16326.68</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>16326.68</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-474.6583721563147</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>13075</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>13075.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>89.74</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>94.45</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>96.92</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>96.92</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>8083.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>8686.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>8686.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>9463.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>16246.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>16246.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-856.7283454234039</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>8083</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>8083.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>90.16000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>94.99</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>97.05</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>97.05</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>12083.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>9101.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>9101.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9314.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>16272.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>16272.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-837.0880091826984</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>12083</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>12083.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>90.52000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>95.45</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>97.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>97.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>8830.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>7839.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>7839.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>9048.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>16275.18</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>16275.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1207.705814225166</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>8830</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>8830.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>95.86</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>97.3</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>95.86</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>97.3</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>9183.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>7315.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>7315.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>9715.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>16371.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>16371.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1345.491756634936</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>9183</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>9183.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15259,11 +15061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>2459</t>
@@ -15445,41 +15243,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr">
         <is>
           <t>0</t>
@@ -15500,20 +15294,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>0</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
